--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-07T11:15:53+00:00</t>
+    <t>2026-05-08T09:03:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:03:17+00:00</t>
+    <t>2026-05-08T09:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T09:31:23+00:00</t>
+    <t>2026-05-08T10:13:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-08T10:13:17+00:00</t>
+    <t>2026-05-11T15:54:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -84,7 +84,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allowed coded values for TimingMetricCodes, generated from enum_models.py.</t>
+    <t>Allowed coded values for TimingMetricCodes</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -250,6 +250,12 @@
   </si>
   <si>
     <t>IV Antihypertensive to Systolic Blood Pressure &lt; 140 mmHg</t>
+  </si>
+  <si>
+    <t>sys-bp-lt-140</t>
+  </si>
+  <si>
+    <t>Systolic Blood Pressure &lt; 140 mmHg</t>
   </si>
   <si>
     <t/>
@@ -522,7 +528,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B28"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -742,15 +748,23 @@
         <v>79</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="B28" t="s" s="2">
         <v>81</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>82</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>83</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:34+00:00</t>
+    <t>2026-05-11T15:54:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:54:44+00:00</t>
+    <t>2026-05-12T07:59:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T07:59:38+00:00</t>
+    <t>2026-05-12T09:41:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T09:41:56+00:00</t>
+    <t>2026-05-12T11:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-12T11:55:23+00:00</t>
+    <t>2026-05-13T14:14:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:14:43+00:00</t>
+    <t>2026-05-13T15:23:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T15:23:44+00:00</t>
+    <t>2026-05-14T08:09:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:09:55+00:00</t>
+    <t>2026-05-14T08:55:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T08:55:50+00:00</t>
+    <t>2026-05-14T09:35:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T09:35:04+00:00</t>
+    <t>2026-05-14T11:02:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-14T11:02:20+00:00</t>
+    <t>2026-05-15T10:10:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T10:10:20+00:00</t>
+    <t>2026-06-01T07:47:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T07:47:29+00:00</t>
+    <t>2026-06-01T10:24:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:24:12+00:00</t>
+    <t>2026-06-01T10:42:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T10:42:50+00:00</t>
+    <t>2026-06-01T12:57:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T12:57:35+00:00</t>
+    <t>2026-06-02T10:42:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T10:42:43+00:00</t>
+    <t>2026-06-03T07:55:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T07:55:03+00:00</t>
+    <t>2026-06-03T14:48:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:48:08+00:00</t>
+    <t>2026-06-03T14:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-03T14:50:23+00:00</t>
+    <t>2026-06-08T09:55:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T09:55:23+00:00</t>
+    <t>2026-06-08T10:51:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T10:51:55+00:00</t>
+    <t>2026-06-08T11:21:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T11:21:15+00:00</t>
+    <t>2026-06-11T11:47:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T11:47:40+00:00</t>
+    <t>2026-06-11T14:44:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-11T14:44:28+00:00</t>
+    <t>2026-06-12T09:34:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T09:34:13+00:00</t>
+    <t>2026-07-01T13:43:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T13:43:23+00:00</t>
+    <t>2026-07-09T09:09:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="88" uniqueCount="86">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -120,10 +120,16 @@
     <t>Door to Groin &lt;= 120 Minutes</t>
   </si>
   <si>
-    <t>D2D</t>
+    <t>Door2Door</t>
   </si>
   <si>
     <t>Door to Door</t>
+  </si>
+  <si>
+    <t>Door2Discharge</t>
+  </si>
+  <si>
+    <t>Door to Discharge</t>
   </si>
   <si>
     <t>D2N</t>
@@ -528,7 +534,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -756,15 +762,23 @@
         <v>81</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B29" t="s" s="2">
         <v>83</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>85</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/timing-metric-codes-vs</t>
+    <t>http://qualityregistry.org/ValueSet/timing-metric-codes-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -72,7 +72,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>
@@ -270,7 +270,7 @@
     <t>System URI</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/CodeSystem/timing-metric-codes-cs</t>
+    <t>http://qualityregistry.org/CodeSystem/timing-metric-codes-cs</t>
   </si>
 </sst>
 </file>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-timing-metric-codes-vs.xlsx
+++ b/ValueSet-timing-metric-codes-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
